--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123331877</v>
+        <v>123331047</v>
       </c>
       <c r="B6" t="n">
-        <v>56680</v>
+        <v>90948</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563737</v>
+        <v>563862</v>
       </c>
       <c r="R6" t="n">
-        <v>7034670</v>
+        <v>7034632</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123331725</v>
+        <v>123331877</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>56680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1261,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563771</v>
+        <v>563737</v>
       </c>
       <c r="R7" t="n">
-        <v>7034644</v>
+        <v>7034670</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123331047</v>
+        <v>123331725</v>
       </c>
       <c r="B8" t="n">
-        <v>90948</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563862</v>
+        <v>563771</v>
       </c>
       <c r="R8" t="n">
-        <v>7034632</v>
+        <v>7034644</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2180,10 +2180,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123330924</v>
+        <v>123332362</v>
       </c>
       <c r="B15" t="n">
-        <v>90948</v>
+        <v>92233</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,38 +2192,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563880</v>
+        <v>563655</v>
       </c>
       <c r="R15" t="n">
-        <v>7034641</v>
+        <v>7034668</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,10 +2292,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123332362</v>
+        <v>123330924</v>
       </c>
       <c r="B16" t="n">
-        <v>92233</v>
+        <v>90948</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563655</v>
+        <v>563880</v>
       </c>
       <c r="R16" t="n">
-        <v>7034668</v>
+        <v>7034641</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123331957</v>
+        <v>123331425</v>
       </c>
       <c r="B20" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,34 +2766,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563744</v>
+        <v>563804</v>
       </c>
       <c r="R20" t="n">
-        <v>7034680</v>
+        <v>7034635</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2825,7 +2830,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,7 +2840,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,10 +2872,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123332312</v>
+        <v>123331957</v>
       </c>
       <c r="B21" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,34 +2888,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563656</v>
+        <v>563744</v>
       </c>
       <c r="R21" t="n">
-        <v>7034674</v>
+        <v>7034680</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123331425</v>
+        <v>123332312</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,39 +3000,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563804</v>
+        <v>563656</v>
       </c>
       <c r="R22" t="n">
-        <v>7034635</v>
+        <v>7034674</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3064,12 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123331047</v>
+        <v>123331877</v>
       </c>
       <c r="B6" t="n">
-        <v>90948</v>
+        <v>56680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563862</v>
+        <v>563737</v>
       </c>
       <c r="R6" t="n">
-        <v>7034632</v>
+        <v>7034670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123331877</v>
+        <v>123331725</v>
       </c>
       <c r="B7" t="n">
-        <v>56680</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563737</v>
+        <v>563771</v>
       </c>
       <c r="R7" t="n">
-        <v>7034670</v>
+        <v>7034644</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123331725</v>
+        <v>123331047</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>90948</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563771</v>
+        <v>563862</v>
       </c>
       <c r="R8" t="n">
-        <v>7034644</v>
+        <v>7034632</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123331877</v>
+        <v>123331047</v>
       </c>
       <c r="B6" t="n">
-        <v>56680</v>
+        <v>90948</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563737</v>
+        <v>563862</v>
       </c>
       <c r="R6" t="n">
-        <v>7034670</v>
+        <v>7034632</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123331725</v>
+        <v>123331877</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>56680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1261,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563771</v>
+        <v>563737</v>
       </c>
       <c r="R7" t="n">
-        <v>7034644</v>
+        <v>7034670</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123331047</v>
+        <v>123331725</v>
       </c>
       <c r="B8" t="n">
-        <v>90948</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563862</v>
+        <v>563771</v>
       </c>
       <c r="R8" t="n">
-        <v>7034632</v>
+        <v>7034644</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2180,10 +2180,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123332362</v>
+        <v>123330924</v>
       </c>
       <c r="B15" t="n">
-        <v>92233</v>
+        <v>90948</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,38 +2192,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563655</v>
+        <v>563880</v>
       </c>
       <c r="R15" t="n">
-        <v>7034668</v>
+        <v>7034641</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,10 +2292,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123330924</v>
+        <v>123332362</v>
       </c>
       <c r="B16" t="n">
-        <v>90948</v>
+        <v>92233</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563880</v>
+        <v>563655</v>
       </c>
       <c r="R16" t="n">
-        <v>7034641</v>
+        <v>7034668</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123331425</v>
+        <v>123331957</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>78502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,39 +2766,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563804</v>
+        <v>563744</v>
       </c>
       <c r="R20" t="n">
-        <v>7034635</v>
+        <v>7034680</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2830,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2840,12 +2835,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,10 +2862,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123331957</v>
+        <v>123332312</v>
       </c>
       <c r="B21" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2888,34 +2878,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563744</v>
+        <v>563656</v>
       </c>
       <c r="R21" t="n">
-        <v>7034680</v>
+        <v>7034674</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2947,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,10 +2974,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123332312</v>
+        <v>123331425</v>
       </c>
       <c r="B22" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3000,34 +2990,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563656</v>
+        <v>563804</v>
       </c>
       <c r="R22" t="n">
-        <v>7034674</v>
+        <v>7034635</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,7 +3054,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3064,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123331364</v>
+        <v>123331877</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>56683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563802</v>
+        <v>563737</v>
       </c>
       <c r="R2" t="n">
-        <v>7034635</v>
+        <v>7034670</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123331875</v>
+        <v>123332256</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563774</v>
+        <v>563690</v>
       </c>
       <c r="R3" t="n">
-        <v>7034678</v>
+        <v>7034661</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333247</v>
+        <v>123331912</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563872</v>
+        <v>563741</v>
       </c>
       <c r="R4" t="n">
-        <v>7034672</v>
+        <v>7034682</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333468</v>
+        <v>123331745</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,37 +1042,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563868</v>
+        <v>563774</v>
       </c>
       <c r="R5" t="n">
-        <v>7034642</v>
+        <v>7034650</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123331047</v>
+        <v>123330924</v>
       </c>
       <c r="B6" t="n">
-        <v>90948</v>
+        <v>90951</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,14 +1179,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563862</v>
+        <v>563880</v>
       </c>
       <c r="R6" t="n">
-        <v>7034632</v>
+        <v>7034641</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123331877</v>
+        <v>123331329</v>
       </c>
       <c r="B7" t="n">
-        <v>56680</v>
+        <v>57497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,16 +1271,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1281,7 +1291,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1290,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563737</v>
+        <v>563811</v>
       </c>
       <c r="R7" t="n">
-        <v>7034670</v>
+        <v>7034627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123331725</v>
+        <v>123332362</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>92236</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1384,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563771</v>
+        <v>563655</v>
       </c>
       <c r="R8" t="n">
-        <v>7034644</v>
+        <v>7034668</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123331745</v>
+        <v>123331425</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,27 +1500,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1519,13 +1529,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563774</v>
+        <v>563804</v>
       </c>
       <c r="R9" t="n">
-        <v>7034650</v>
+        <v>7034635</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1574,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,22 +1594,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333420</v>
+        <v>123331199</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,42 +1618,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563874</v>
+        <v>563848</v>
       </c>
       <c r="R10" t="n">
-        <v>7034649</v>
+        <v>7034634</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123332733</v>
+        <v>123331957</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78505</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,39 +1734,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563800</v>
+        <v>563744</v>
       </c>
       <c r="R11" t="n">
-        <v>7034674</v>
+        <v>7034680</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,12 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123331329</v>
+        <v>123331795</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>78769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,39 +1846,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563811</v>
+        <v>563756</v>
       </c>
       <c r="R12" t="n">
-        <v>7034627</v>
+        <v>7034671</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123331912</v>
+        <v>123333468</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>90955</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,21 +1958,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1986,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563741</v>
+        <v>563868</v>
       </c>
       <c r="R13" t="n">
-        <v>7034682</v>
+        <v>7034642</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2027,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123331993</v>
+        <v>123333420</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>98368</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,31 +2066,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2103,10 +2098,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563779</v>
+        <v>563874</v>
       </c>
       <c r="R14" t="n">
-        <v>7034696</v>
+        <v>7034649</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,12 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,22 +2158,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123330924</v>
+        <v>123331875</v>
       </c>
       <c r="B15" t="n">
-        <v>90948</v>
+        <v>90973</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2196,21 +2186,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2220,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563880</v>
+        <v>563774</v>
       </c>
       <c r="R15" t="n">
-        <v>7034641</v>
+        <v>7034678</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2265,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,22 +2270,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123332362</v>
+        <v>123331725</v>
       </c>
       <c r="B16" t="n">
-        <v>92233</v>
+        <v>78769</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2304,25 +2294,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2332,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563655</v>
+        <v>563771</v>
       </c>
       <c r="R16" t="n">
-        <v>7034668</v>
+        <v>7034644</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2367,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,10 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123332192</v>
+        <v>123331047</v>
       </c>
       <c r="B17" t="n">
-        <v>92233</v>
+        <v>90951</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,25 +2406,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2444,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563700</v>
+        <v>563862</v>
       </c>
       <c r="R17" t="n">
-        <v>7034666</v>
+        <v>7034632</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123332256</v>
+        <v>123333247</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,39 +2522,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563690</v>
+        <v>563872</v>
       </c>
       <c r="R18" t="n">
-        <v>7034661</v>
+        <v>7034672</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2596,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,12 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2638,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123331795</v>
+        <v>123332192</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>92236</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2650,38 +2630,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563756</v>
+        <v>563700</v>
       </c>
       <c r="R19" t="n">
-        <v>7034671</v>
+        <v>7034666</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2713,7 +2693,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2723,7 +2703,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2750,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123331957</v>
+        <v>123332312</v>
       </c>
       <c r="B20" t="n">
-        <v>78502</v>
+        <v>78506</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,34 +2746,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563744</v>
+        <v>563656</v>
       </c>
       <c r="R20" t="n">
-        <v>7034680</v>
+        <v>7034674</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2825,7 +2805,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,7 +2815,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,10 +2842,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123332312</v>
+        <v>123331364</v>
       </c>
       <c r="B21" t="n">
-        <v>78503</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,34 +2858,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563656</v>
+        <v>563802</v>
       </c>
       <c r="R21" t="n">
-        <v>7034674</v>
+        <v>7034635</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2932,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,10 +2964,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123331425</v>
+        <v>123332733</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3010,19 +3000,19 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563804</v>
+        <v>563800</v>
       </c>
       <c r="R22" t="n">
-        <v>7034635</v>
+        <v>7034674</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,7 +3044,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3064,12 +3054,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,10 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123331199</v>
+        <v>123331993</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3112,34 +3102,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563848</v>
+        <v>563779</v>
       </c>
       <c r="R23" t="n">
-        <v>7034634</v>
+        <v>7034696</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3171,7 +3166,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3176,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,12 +3196,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123331877</v>
+        <v>123333247</v>
       </c>
       <c r="B2" t="n">
-        <v>56683</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563737</v>
+        <v>563872</v>
       </c>
       <c r="R2" t="n">
-        <v>7034670</v>
+        <v>7034672</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332256</v>
+        <v>123331745</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,27 +803,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563690</v>
+        <v>563774</v>
       </c>
       <c r="R3" t="n">
-        <v>7034661</v>
+        <v>7034650</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123331912</v>
+        <v>123331329</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563741</v>
+        <v>563811</v>
       </c>
       <c r="R4" t="n">
-        <v>7034682</v>
+        <v>7034627</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123331745</v>
+        <v>123331199</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
+        <v>78771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,42 +1037,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563774</v>
+        <v>563848</v>
       </c>
       <c r="R5" t="n">
-        <v>7034650</v>
+        <v>7034634</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123330924</v>
+        <v>123331957</v>
       </c>
       <c r="B6" t="n">
-        <v>90951</v>
+        <v>78507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563880</v>
+        <v>563744</v>
       </c>
       <c r="R6" t="n">
-        <v>7034641</v>
+        <v>7034680</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123331329</v>
+        <v>123332256</v>
       </c>
       <c r="B7" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,16 +1261,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1291,7 +1281,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1300,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563811</v>
+        <v>563690</v>
       </c>
       <c r="R7" t="n">
-        <v>7034627</v>
+        <v>7034661</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1335,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123332362</v>
+        <v>123333420</v>
       </c>
       <c r="B8" t="n">
-        <v>92236</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,38 +1379,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563655</v>
+        <v>563874</v>
       </c>
       <c r="R8" t="n">
-        <v>7034668</v>
+        <v>7034649</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,7 +1483,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123331425</v>
+        <v>123332733</v>
       </c>
       <c r="B9" t="n">
         <v>57481</v>
@@ -1520,19 +1519,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563804</v>
+        <v>563800</v>
       </c>
       <c r="R9" t="n">
-        <v>7034635</v>
+        <v>7034674</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,12 +1573,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123331199</v>
+        <v>123331993</v>
       </c>
       <c r="B10" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,34 +1621,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563848</v>
+        <v>563779</v>
       </c>
       <c r="R10" t="n">
-        <v>7034634</v>
+        <v>7034696</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1695,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,22 +1715,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123331957</v>
+        <v>123331875</v>
       </c>
       <c r="B11" t="n">
-        <v>78505</v>
+        <v>90975</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,21 +1743,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1758,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563744</v>
+        <v>563774</v>
       </c>
       <c r="R11" t="n">
-        <v>7034680</v>
+        <v>7034678</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1812,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,22 +1827,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123331795</v>
+        <v>123331725</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,14 +1875,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563756</v>
+        <v>563771</v>
       </c>
       <c r="R12" t="n">
-        <v>7034671</v>
+        <v>7034644</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1914,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1924,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1951,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333468</v>
+        <v>123332312</v>
       </c>
       <c r="B13" t="n">
-        <v>90955</v>
+        <v>78508</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,34 +1967,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563868</v>
+        <v>563656</v>
       </c>
       <c r="R13" t="n">
-        <v>7034642</v>
+        <v>7034674</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333420</v>
+        <v>123331912</v>
       </c>
       <c r="B14" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,42 +2075,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563874</v>
+        <v>563741</v>
       </c>
       <c r="R14" t="n">
-        <v>7034649</v>
+        <v>7034682</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,7 +2138,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2148,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,10 +2175,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123331875</v>
+        <v>123332192</v>
       </c>
       <c r="B15" t="n">
-        <v>90973</v>
+        <v>92238</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,38 +2187,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563774</v>
+        <v>563700</v>
       </c>
       <c r="R15" t="n">
-        <v>7034678</v>
+        <v>7034666</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2260,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,22 +2275,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123331725</v>
+        <v>123332362</v>
       </c>
       <c r="B16" t="n">
-        <v>78769</v>
+        <v>92238</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,25 +2299,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2322,10 +2327,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563771</v>
+        <v>563655</v>
       </c>
       <c r="R16" t="n">
-        <v>7034644</v>
+        <v>7034668</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123331047</v>
+        <v>123330924</v>
       </c>
       <c r="B17" t="n">
-        <v>90951</v>
+        <v>90953</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,14 +2435,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563862</v>
+        <v>563880</v>
       </c>
       <c r="R17" t="n">
-        <v>7034632</v>
+        <v>7034641</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2484,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123333247</v>
+        <v>123331877</v>
       </c>
       <c r="B18" t="n">
-        <v>78769</v>
+        <v>56683</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2522,34 +2527,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563872</v>
+        <v>563737</v>
       </c>
       <c r="R18" t="n">
-        <v>7034672</v>
+        <v>7034670</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123332192</v>
+        <v>123331047</v>
       </c>
       <c r="B19" t="n">
-        <v>92236</v>
+        <v>90953</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,25 +2640,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2658,10 +2668,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563700</v>
+        <v>563862</v>
       </c>
       <c r="R19" t="n">
-        <v>7034666</v>
+        <v>7034632</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2693,7 +2703,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2703,7 +2713,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,10 +2740,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123332312</v>
+        <v>123333468</v>
       </c>
       <c r="B20" t="n">
-        <v>78506</v>
+        <v>90957</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2746,34 +2756,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563656</v>
+        <v>563868</v>
       </c>
       <c r="R20" t="n">
-        <v>7034674</v>
+        <v>7034642</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2805,7 +2815,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2815,7 +2825,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2842,7 +2852,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123331364</v>
+        <v>123331425</v>
       </c>
       <c r="B21" t="n">
         <v>57481</v>
@@ -2878,7 +2888,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2887,7 +2897,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563802</v>
+        <v>563804</v>
       </c>
       <c r="R21" t="n">
         <v>7034635</v>
@@ -2922,7 +2932,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,7 +2942,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2964,7 +2974,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123332733</v>
+        <v>123331364</v>
       </c>
       <c r="B22" t="n">
         <v>57481</v>
@@ -3005,14 +3015,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563800</v>
+        <v>563802</v>
       </c>
       <c r="R22" t="n">
-        <v>7034674</v>
+        <v>7034635</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3044,7 +3054,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3054,12 +3064,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3086,10 +3096,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123331993</v>
+        <v>123331795</v>
       </c>
       <c r="B23" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,39 +3112,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563779</v>
+        <v>563756</v>
       </c>
       <c r="R23" t="n">
-        <v>7034696</v>
+        <v>7034671</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3166,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3176,12 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,12 +3196,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -2063,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123331912</v>
+        <v>123332192</v>
       </c>
       <c r="B14" t="n">
-        <v>78771</v>
+        <v>92238</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2075,38 +2075,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563741</v>
+        <v>563700</v>
       </c>
       <c r="R14" t="n">
-        <v>7034682</v>
+        <v>7034666</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,10 +2175,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123332192</v>
+        <v>123331912</v>
       </c>
       <c r="B15" t="n">
-        <v>92238</v>
+        <v>78771</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,38 +2187,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563700</v>
+        <v>563741</v>
       </c>
       <c r="R15" t="n">
-        <v>7034666</v>
+        <v>7034682</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333247</v>
+        <v>123332256</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563872</v>
+        <v>563690</v>
       </c>
       <c r="R2" t="n">
-        <v>7034672</v>
+        <v>7034661</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123331745</v>
+        <v>123331047</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>90959</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +813,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563774</v>
+        <v>563862</v>
       </c>
       <c r="R3" t="n">
-        <v>7034650</v>
+        <v>7034632</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123331329</v>
+        <v>123331199</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563811</v>
+        <v>563848</v>
       </c>
       <c r="R4" t="n">
-        <v>7034627</v>
+        <v>7034634</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123331199</v>
+        <v>123331875</v>
       </c>
       <c r="B5" t="n">
-        <v>78771</v>
+        <v>90981</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563848</v>
+        <v>563774</v>
       </c>
       <c r="R5" t="n">
-        <v>7034634</v>
+        <v>7034678</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123331957</v>
+        <v>123332312</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
+        <v>78509</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563744</v>
+        <v>563656</v>
       </c>
       <c r="R6" t="n">
-        <v>7034680</v>
+        <v>7034674</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123332256</v>
+        <v>123331725</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563690</v>
+        <v>563771</v>
       </c>
       <c r="R7" t="n">
-        <v>7034661</v>
+        <v>7034644</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,12 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333420</v>
+        <v>123331957</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>78508</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,42 +1369,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563874</v>
+        <v>563744</v>
       </c>
       <c r="R8" t="n">
-        <v>7034649</v>
+        <v>7034680</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123332733</v>
+        <v>123332192</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>92244</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,43 +1481,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563800</v>
+        <v>563700</v>
       </c>
       <c r="R9" t="n">
-        <v>7034674</v>
+        <v>7034666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,12 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123331993</v>
+        <v>123332362</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>92244</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,43 +1593,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563779</v>
+        <v>563655</v>
       </c>
       <c r="R10" t="n">
-        <v>7034696</v>
+        <v>7034668</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,12 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,22 +1681,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123331875</v>
+        <v>123333468</v>
       </c>
       <c r="B11" t="n">
-        <v>90975</v>
+        <v>90963</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,21 +1709,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1767,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563774</v>
+        <v>563868</v>
       </c>
       <c r="R11" t="n">
-        <v>7034678</v>
+        <v>7034642</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,22 +1793,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123331725</v>
+        <v>123330924</v>
       </c>
       <c r="B12" t="n">
-        <v>78771</v>
+        <v>90959</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,34 +1821,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563771</v>
+        <v>563880</v>
       </c>
       <c r="R12" t="n">
-        <v>7034644</v>
+        <v>7034641</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1924,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123332312</v>
+        <v>123331795</v>
       </c>
       <c r="B13" t="n">
-        <v>78508</v>
+        <v>78772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1967,34 +1933,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563656</v>
+        <v>563756</v>
       </c>
       <c r="R13" t="n">
-        <v>7034674</v>
+        <v>7034671</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123332192</v>
+        <v>123332733</v>
       </c>
       <c r="B14" t="n">
-        <v>92238</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2075,38 +2041,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563700</v>
+        <v>563800</v>
       </c>
       <c r="R14" t="n">
-        <v>7034666</v>
+        <v>7034674</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,7 +2119,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,7 +2154,7 @@
         <v>123331912</v>
       </c>
       <c r="B15" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2287,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123332362</v>
+        <v>123333247</v>
       </c>
       <c r="B16" t="n">
-        <v>92238</v>
+        <v>78772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2299,38 +2275,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563655</v>
+        <v>563872</v>
       </c>
       <c r="R16" t="n">
-        <v>7034668</v>
+        <v>7034672</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2375,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123330924</v>
+        <v>123331877</v>
       </c>
       <c r="B17" t="n">
-        <v>90953</v>
+        <v>56683</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,34 +2391,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563880</v>
+        <v>563737</v>
       </c>
       <c r="R17" t="n">
-        <v>7034641</v>
+        <v>7034670</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2474,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123331877</v>
+        <v>123331993</v>
       </c>
       <c r="B18" t="n">
-        <v>56683</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,16 +2508,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2547,19 +2528,19 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563737</v>
+        <v>563779</v>
       </c>
       <c r="R18" t="n">
-        <v>7034670</v>
+        <v>7034696</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,7 +2582,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,22 +2602,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123331047</v>
+        <v>123331329</v>
       </c>
       <c r="B19" t="n">
-        <v>90953</v>
+        <v>57497</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,34 +2630,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563862</v>
+        <v>563811</v>
       </c>
       <c r="R19" t="n">
-        <v>7034632</v>
+        <v>7034627</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2703,7 +2694,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2713,7 +2704,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,10 +2731,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123333468</v>
+        <v>123331425</v>
       </c>
       <c r="B20" t="n">
-        <v>90957</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2756,34 +2747,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563868</v>
+        <v>563804</v>
       </c>
       <c r="R20" t="n">
-        <v>7034642</v>
+        <v>7034635</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,7 +2811,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2825,7 +2821,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,7 +2853,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123331425</v>
+        <v>123331364</v>
       </c>
       <c r="B21" t="n">
         <v>57481</v>
@@ -2888,7 +2889,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2897,7 +2898,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563804</v>
+        <v>563802</v>
       </c>
       <c r="R21" t="n">
         <v>7034635</v>
@@ -2932,7 +2933,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2942,7 +2943,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2974,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123331364</v>
+        <v>123333420</v>
       </c>
       <c r="B22" t="n">
-        <v>57481</v>
+        <v>98376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2986,43 +2987,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563802</v>
+        <v>563874</v>
       </c>
       <c r="R22" t="n">
-        <v>7034635</v>
+        <v>7034649</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3064,12 +3064,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,10 +3091,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123331795</v>
+        <v>123331745</v>
       </c>
       <c r="B23" t="n">
-        <v>78771</v>
+        <v>57634</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3112,37 +3107,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563756</v>
+        <v>563774</v>
       </c>
       <c r="R23" t="n">
-        <v>7034671</v>
+        <v>7034650</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,12 +3196,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123331993</v>
+        <v>123330924</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>90979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563779</v>
+        <v>563880</v>
       </c>
       <c r="R2" t="n">
-        <v>7034696</v>
+        <v>7034641</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123331912</v>
+        <v>123332312</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78518</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563741</v>
+        <v>563656</v>
       </c>
       <c r="R3" t="n">
-        <v>7034682</v>
+        <v>7034674</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123332312</v>
+        <v>123332362</v>
       </c>
       <c r="B4" t="n">
-        <v>78512</v>
+        <v>92264</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563656</v>
+        <v>563655</v>
       </c>
       <c r="R4" t="n">
-        <v>7034674</v>
+        <v>7034668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123331957</v>
+        <v>123331425</v>
       </c>
       <c r="B5" t="n">
-        <v>78511</v>
+        <v>57487</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563744</v>
+        <v>563804</v>
       </c>
       <c r="R5" t="n">
-        <v>7034680</v>
+        <v>7034635</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123331329</v>
+        <v>123331199</v>
       </c>
       <c r="B6" t="n">
-        <v>57497</v>
+        <v>78781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563811</v>
+        <v>563848</v>
       </c>
       <c r="R6" t="n">
-        <v>7034627</v>
+        <v>7034634</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123331364</v>
+        <v>123331993</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,19 +1281,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563802</v>
+        <v>563779</v>
       </c>
       <c r="R7" t="n">
-        <v>7034635</v>
+        <v>7034696</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,12 +1335,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,22 +1355,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123331745</v>
+        <v>123331795</v>
       </c>
       <c r="B8" t="n">
-        <v>57634</v>
+        <v>78781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,42 +1383,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563774</v>
+        <v>563756</v>
       </c>
       <c r="R8" t="n">
-        <v>7034650</v>
+        <v>7034671</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123331425</v>
+        <v>123331364</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,7 +1515,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1534,7 +1524,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563804</v>
+        <v>563802</v>
       </c>
       <c r="R9" t="n">
         <v>7034635</v>
@@ -1569,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1611,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123331199</v>
+        <v>123331745</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>57640</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,37 +1617,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563848</v>
+        <v>563774</v>
       </c>
       <c r="R10" t="n">
-        <v>7034634</v>
+        <v>7034650</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1686,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,22 +1706,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123331795</v>
+        <v>123332192</v>
       </c>
       <c r="B11" t="n">
-        <v>78775</v>
+        <v>92264</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,38 +1730,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563756</v>
+        <v>563700</v>
       </c>
       <c r="R11" t="n">
-        <v>7034671</v>
+        <v>7034666</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333420</v>
+        <v>123331047</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>90979</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,42 +1842,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563874</v>
+        <v>563862</v>
       </c>
       <c r="R12" t="n">
-        <v>7034649</v>
+        <v>7034632</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1924,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123331877</v>
+        <v>123332733</v>
       </c>
       <c r="B13" t="n">
-        <v>56683</v>
+        <v>57487</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1967,16 +1958,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1987,19 +1978,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563737</v>
+        <v>563800</v>
       </c>
       <c r="R13" t="n">
-        <v>7034670</v>
+        <v>7034674</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2041,7 +2032,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2068,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333468</v>
+        <v>123331877</v>
       </c>
       <c r="B14" t="n">
-        <v>90966</v>
+        <v>56689</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2084,34 +2080,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563868</v>
+        <v>563737</v>
       </c>
       <c r="R14" t="n">
-        <v>7034642</v>
+        <v>7034670</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,7 +2144,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2153,7 +2154,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2180,10 +2181,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123331047</v>
+        <v>123331329</v>
       </c>
       <c r="B15" t="n">
-        <v>90962</v>
+        <v>57503</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2196,34 +2197,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563862</v>
+        <v>563811</v>
       </c>
       <c r="R15" t="n">
-        <v>7034632</v>
+        <v>7034627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,7 +2261,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2265,7 +2271,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,10 +2298,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333247</v>
+        <v>123331725</v>
       </c>
       <c r="B16" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,14 +2334,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563872</v>
+        <v>563771</v>
       </c>
       <c r="R16" t="n">
-        <v>7034672</v>
+        <v>7034644</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,7 +2373,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2383,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,10 +2410,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123332192</v>
+        <v>123331875</v>
       </c>
       <c r="B17" t="n">
-        <v>92247</v>
+        <v>91001</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,38 +2422,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563700</v>
+        <v>563774</v>
       </c>
       <c r="R17" t="n">
-        <v>7034666</v>
+        <v>7034678</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,7 +2485,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2495,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,22 +2510,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123332362</v>
+        <v>123332256</v>
       </c>
       <c r="B18" t="n">
-        <v>92247</v>
+        <v>57487</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,38 +2534,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563655</v>
+        <v>563690</v>
       </c>
       <c r="R18" t="n">
-        <v>7034668</v>
+        <v>7034661</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2602,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,7 +2612,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,10 +2644,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123332256</v>
+        <v>123333468</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
+        <v>90983</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,39 +2660,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563690</v>
+        <v>563868</v>
       </c>
       <c r="R19" t="n">
-        <v>7034661</v>
+        <v>7034642</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2708,7 +2719,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,12 +2729,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2750,10 +2756,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123332733</v>
+        <v>123331912</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,39 +2772,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563800</v>
+        <v>563741</v>
       </c>
       <c r="R20" t="n">
-        <v>7034674</v>
+        <v>7034682</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2830,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2840,12 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123330924</v>
+        <v>123333420</v>
       </c>
       <c r="B21" t="n">
-        <v>90962</v>
+        <v>98396</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2884,38 +2880,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563880</v>
+        <v>563874</v>
       </c>
       <c r="R21" t="n">
-        <v>7034641</v>
+        <v>7034649</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123331725</v>
+        <v>123331957</v>
       </c>
       <c r="B22" t="n">
-        <v>78775</v>
+        <v>78517</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3000,34 +3000,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563771</v>
+        <v>563744</v>
       </c>
       <c r="R22" t="n">
-        <v>7034644</v>
+        <v>7034680</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,10 +3096,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123331875</v>
+        <v>123333247</v>
       </c>
       <c r="B23" t="n">
-        <v>90984</v>
+        <v>78781</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3112,21 +3112,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563774</v>
+        <v>563872</v>
       </c>
       <c r="R23" t="n">
-        <v>7034678</v>
+        <v>7034672</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,12 +3196,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -2064,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123331877</v>
+        <v>123331329</v>
       </c>
       <c r="B14" t="n">
-        <v>56689</v>
+        <v>57503</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2100,7 +2100,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563737</v>
+        <v>563811</v>
       </c>
       <c r="R14" t="n">
-        <v>7034670</v>
+        <v>7034627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,10 +2181,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123331329</v>
+        <v>123331877</v>
       </c>
       <c r="B15" t="n">
-        <v>57503</v>
+        <v>56689</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,16 +2197,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2217,7 +2217,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563811</v>
+        <v>563737</v>
       </c>
       <c r="R15" t="n">
-        <v>7034627</v>
+        <v>7034670</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2868,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123333420</v>
+        <v>123331957</v>
       </c>
       <c r="B21" t="n">
-        <v>98396</v>
+        <v>78517</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2880,42 +2880,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563874</v>
+        <v>563744</v>
       </c>
       <c r="R21" t="n">
-        <v>7034649</v>
+        <v>7034680</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2947,7 +2943,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2953,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,10 +2980,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123331957</v>
+        <v>123333420</v>
       </c>
       <c r="B22" t="n">
-        <v>78517</v>
+        <v>98396</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2996,38 +2992,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563744</v>
+        <v>563874</v>
       </c>
       <c r="R22" t="n">
-        <v>7034680</v>
+        <v>7034649</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123330924</v>
+        <v>123331047</v>
       </c>
       <c r="B2" t="n">
-        <v>90979</v>
+        <v>90984</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563880</v>
+        <v>563862</v>
       </c>
       <c r="R2" t="n">
-        <v>7034641</v>
+        <v>7034632</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332312</v>
+        <v>123331957</v>
       </c>
       <c r="B3" t="n">
-        <v>78518</v>
+        <v>78522</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563656</v>
+        <v>563744</v>
       </c>
       <c r="R3" t="n">
-        <v>7034674</v>
+        <v>7034680</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123332362</v>
+        <v>123331993</v>
       </c>
       <c r="B4" t="n">
-        <v>92264</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +911,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563655</v>
+        <v>563779</v>
       </c>
       <c r="R4" t="n">
-        <v>7034668</v>
+        <v>7034696</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123331425</v>
+        <v>123332256</v>
       </c>
       <c r="B5" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563804</v>
+        <v>563690</v>
       </c>
       <c r="R5" t="n">
-        <v>7034635</v>
+        <v>7034661</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123331199</v>
+        <v>123331725</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563848</v>
+        <v>563771</v>
       </c>
       <c r="R6" t="n">
-        <v>7034634</v>
+        <v>7034644</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123331993</v>
+        <v>123331877</v>
       </c>
       <c r="B7" t="n">
-        <v>57487</v>
+        <v>56692</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,16 +1271,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1281,19 +1291,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563779</v>
+        <v>563737</v>
       </c>
       <c r="R7" t="n">
-        <v>7034696</v>
+        <v>7034670</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,12 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,22 +1360,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123331795</v>
+        <v>123331912</v>
       </c>
       <c r="B8" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563756</v>
+        <v>563741</v>
       </c>
       <c r="R8" t="n">
-        <v>7034671</v>
+        <v>7034682</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123331364</v>
+        <v>123331875</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>91006</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,39 +1500,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563802</v>
+        <v>563774</v>
       </c>
       <c r="R9" t="n">
-        <v>7034635</v>
+        <v>7034678</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,12 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,22 +1584,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123331745</v>
+        <v>123332312</v>
       </c>
       <c r="B10" t="n">
-        <v>57640</v>
+        <v>78523</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,42 +1612,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563774</v>
+        <v>563656</v>
       </c>
       <c r="R10" t="n">
-        <v>7034650</v>
+        <v>7034674</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1681,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,22 +1696,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123332192</v>
+        <v>123331199</v>
       </c>
       <c r="B11" t="n">
-        <v>92264</v>
+        <v>78786</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,25 +1720,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1758,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563700</v>
+        <v>563848</v>
       </c>
       <c r="R11" t="n">
-        <v>7034666</v>
+        <v>7034634</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123331047</v>
+        <v>123333468</v>
       </c>
       <c r="B12" t="n">
-        <v>90979</v>
+        <v>90988</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,34 +1836,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563862</v>
+        <v>563868</v>
       </c>
       <c r="R12" t="n">
-        <v>7034632</v>
+        <v>7034642</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123332733</v>
+        <v>123331745</v>
       </c>
       <c r="B13" t="n">
-        <v>57487</v>
+        <v>57643</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,42 +1948,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563800</v>
+        <v>563774</v>
       </c>
       <c r="R13" t="n">
-        <v>7034674</v>
+        <v>7034650</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2022,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,12 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,22 +2037,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123331329</v>
+        <v>123333247</v>
       </c>
       <c r="B14" t="n">
-        <v>57503</v>
+        <v>78786</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,39 +2065,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563811</v>
+        <v>563872</v>
       </c>
       <c r="R14" t="n">
-        <v>7034627</v>
+        <v>7034672</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2144,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2154,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,10 +2161,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123331877</v>
+        <v>123332192</v>
       </c>
       <c r="B15" t="n">
-        <v>56689</v>
+        <v>92269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2193,43 +2173,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563737</v>
+        <v>563700</v>
       </c>
       <c r="R15" t="n">
-        <v>7034670</v>
+        <v>7034666</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2261,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2271,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2298,10 +2273,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123331725</v>
+        <v>123331329</v>
       </c>
       <c r="B16" t="n">
-        <v>78781</v>
+        <v>57506</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2314,34 +2289,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563771</v>
+        <v>563811</v>
       </c>
       <c r="R16" t="n">
-        <v>7034644</v>
+        <v>7034627</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2373,7 +2353,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2363,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,10 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123331875</v>
+        <v>123332362</v>
       </c>
       <c r="B17" t="n">
-        <v>91001</v>
+        <v>92269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,38 +2402,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563774</v>
+        <v>563655</v>
       </c>
       <c r="R17" t="n">
-        <v>7034678</v>
+        <v>7034668</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2485,7 +2465,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2495,7 +2475,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2510,22 +2490,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123332256</v>
+        <v>123330924</v>
       </c>
       <c r="B18" t="n">
-        <v>57487</v>
+        <v>90984</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2538,39 +2518,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563690</v>
+        <v>563880</v>
       </c>
       <c r="R18" t="n">
-        <v>7034661</v>
+        <v>7034641</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2602,7 +2577,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2612,12 +2587,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2644,10 +2614,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123333468</v>
+        <v>123333420</v>
       </c>
       <c r="B19" t="n">
-        <v>90983</v>
+        <v>98502</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2656,38 +2626,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563868</v>
+        <v>563874</v>
       </c>
       <c r="R19" t="n">
-        <v>7034642</v>
+        <v>7034649</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2719,7 +2693,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2729,7 +2703,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123331912</v>
+        <v>123331795</v>
       </c>
       <c r="B20" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2796,10 +2770,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563741</v>
+        <v>563756</v>
       </c>
       <c r="R20" t="n">
-        <v>7034682</v>
+        <v>7034671</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2805,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2815,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,10 +2842,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123331957</v>
+        <v>123331425</v>
       </c>
       <c r="B21" t="n">
-        <v>78517</v>
+        <v>57490</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2884,34 +2858,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563744</v>
+        <v>563804</v>
       </c>
       <c r="R21" t="n">
-        <v>7034680</v>
+        <v>7034635</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2943,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2953,7 +2932,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2980,10 +2964,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123333420</v>
+        <v>123331364</v>
       </c>
       <c r="B22" t="n">
-        <v>98396</v>
+        <v>57490</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2992,42 +2976,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563874</v>
+        <v>563802</v>
       </c>
       <c r="R22" t="n">
-        <v>7034649</v>
+        <v>7034635</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,7 +3044,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3054,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,10 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123333247</v>
+        <v>123332733</v>
       </c>
       <c r="B23" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3112,34 +3102,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563872</v>
+        <v>563800</v>
       </c>
       <c r="R23" t="n">
-        <v>7034672</v>
+        <v>7034674</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3171,7 +3166,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3176,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123331047</v>
+        <v>123331745</v>
       </c>
       <c r="B2" t="n">
-        <v>90984</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563862</v>
+        <v>563774</v>
       </c>
       <c r="R2" t="n">
-        <v>7034632</v>
+        <v>7034650</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +780,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,7 +795,7 @@
         <v>123331957</v>
       </c>
       <c r="B3" t="n">
-        <v>78522</v>
+        <v>78524</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123331993</v>
+        <v>123331877</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
+        <v>56692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,16 +920,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,19 +940,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563779</v>
+        <v>563737</v>
       </c>
       <c r="R4" t="n">
-        <v>7034696</v>
+        <v>7034670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123332256</v>
+        <v>123331364</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563690</v>
+        <v>563802</v>
       </c>
       <c r="R5" t="n">
-        <v>7034661</v>
+        <v>7034635</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123331725</v>
+        <v>123332312</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>78525</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563771</v>
+        <v>563656</v>
       </c>
       <c r="R6" t="n">
-        <v>7034644</v>
+        <v>7034674</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123331877</v>
+        <v>123331047</v>
       </c>
       <c r="B7" t="n">
-        <v>56692</v>
+        <v>90986</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,39 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563737</v>
+        <v>563862</v>
       </c>
       <c r="R7" t="n">
-        <v>7034670</v>
+        <v>7034632</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123331912</v>
+        <v>123332192</v>
       </c>
       <c r="B8" t="n">
-        <v>78786</v>
+        <v>92271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,38 +1379,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563741</v>
+        <v>563700</v>
       </c>
       <c r="R8" t="n">
-        <v>7034682</v>
+        <v>7034666</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123331875</v>
+        <v>123333247</v>
       </c>
       <c r="B9" t="n">
-        <v>91006</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1524,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563774</v>
+        <v>563872</v>
       </c>
       <c r="R9" t="n">
-        <v>7034678</v>
+        <v>7034672</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,22 +1579,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123332312</v>
+        <v>123331425</v>
       </c>
       <c r="B10" t="n">
-        <v>78523</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,34 +1607,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563656</v>
+        <v>563804</v>
       </c>
       <c r="R10" t="n">
-        <v>7034674</v>
+        <v>7034635</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1681,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123331199</v>
+        <v>123332733</v>
       </c>
       <c r="B11" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,34 +1729,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563848</v>
+        <v>563800</v>
       </c>
       <c r="R11" t="n">
-        <v>7034634</v>
+        <v>7034674</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1803,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333468</v>
+        <v>123331993</v>
       </c>
       <c r="B12" t="n">
-        <v>90988</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,34 +1851,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563868</v>
+        <v>563779</v>
       </c>
       <c r="R12" t="n">
-        <v>7034642</v>
+        <v>7034696</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1925,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,22 +1945,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123331745</v>
+        <v>123331199</v>
       </c>
       <c r="B13" t="n">
-        <v>57643</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,42 +1973,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563774</v>
+        <v>563848</v>
       </c>
       <c r="R13" t="n">
-        <v>7034650</v>
+        <v>7034634</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2012,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,22 +2057,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333247</v>
+        <v>123333420</v>
       </c>
       <c r="B14" t="n">
-        <v>78786</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,38 +2081,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563872</v>
+        <v>563874</v>
       </c>
       <c r="R14" t="n">
-        <v>7034672</v>
+        <v>7034649</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2158,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123332192</v>
+        <v>123331795</v>
       </c>
       <c r="B15" t="n">
-        <v>92269</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,38 +2197,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563700</v>
+        <v>563756</v>
       </c>
       <c r="R15" t="n">
-        <v>7034666</v>
+        <v>7034671</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2260,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2270,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123331329</v>
+        <v>123332256</v>
       </c>
       <c r="B16" t="n">
-        <v>57506</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2289,16 +2313,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2309,7 +2333,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2318,10 +2342,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563811</v>
+        <v>563690</v>
       </c>
       <c r="R16" t="n">
-        <v>7034627</v>
+        <v>7034661</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,7 +2377,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2363,7 +2387,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,10 +2419,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123332362</v>
+        <v>123333468</v>
       </c>
       <c r="B17" t="n">
-        <v>92269</v>
+        <v>90990</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,38 +2431,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563655</v>
+        <v>563868</v>
       </c>
       <c r="R17" t="n">
-        <v>7034668</v>
+        <v>7034642</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,7 +2494,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2475,7 +2504,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,10 +2531,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123330924</v>
+        <v>123331725</v>
       </c>
       <c r="B18" t="n">
-        <v>90984</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2518,34 +2547,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563880</v>
+        <v>563771</v>
       </c>
       <c r="R18" t="n">
-        <v>7034641</v>
+        <v>7034644</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2577,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2587,7 +2616,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2614,10 +2643,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123333420</v>
+        <v>123331912</v>
       </c>
       <c r="B19" t="n">
-        <v>98502</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2626,42 +2655,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563874</v>
+        <v>563741</v>
       </c>
       <c r="R19" t="n">
-        <v>7034649</v>
+        <v>7034682</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2693,7 +2718,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2703,7 +2728,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,10 +2755,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123331795</v>
+        <v>123331875</v>
       </c>
       <c r="B20" t="n">
-        <v>78786</v>
+        <v>91008</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2746,21 +2771,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2770,10 +2795,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563756</v>
+        <v>563774</v>
       </c>
       <c r="R20" t="n">
-        <v>7034671</v>
+        <v>7034678</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2830,22 +2855,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123331425</v>
+        <v>123331329</v>
       </c>
       <c r="B21" t="n">
-        <v>57490</v>
+        <v>57507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2858,16 +2883,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2878,7 +2903,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2887,10 +2912,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563804</v>
+        <v>563811</v>
       </c>
       <c r="R21" t="n">
-        <v>7034635</v>
+        <v>7034627</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2922,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,12 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2964,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123331364</v>
+        <v>123332362</v>
       </c>
       <c r="B22" t="n">
-        <v>57490</v>
+        <v>92271</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2976,43 +2996,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563802</v>
+        <v>563655</v>
       </c>
       <c r="R22" t="n">
-        <v>7034635</v>
+        <v>7034668</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3044,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3054,12 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3086,10 +3096,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123332733</v>
+        <v>123330924</v>
       </c>
       <c r="B23" t="n">
-        <v>57490</v>
+        <v>90986</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,39 +3112,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563800</v>
+        <v>563880</v>
       </c>
       <c r="R23" t="n">
-        <v>7034674</v>
+        <v>7034641</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3166,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3176,12 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123331364</v>
+        <v>123332312</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>78525</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563802</v>
+        <v>563656</v>
       </c>
       <c r="R5" t="n">
-        <v>7034635</v>
+        <v>7034674</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123332312</v>
+        <v>123331364</v>
       </c>
       <c r="B6" t="n">
-        <v>78525</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563656</v>
+        <v>563802</v>
       </c>
       <c r="R6" t="n">
-        <v>7034674</v>
+        <v>7034635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333247</v>
+        <v>123331425</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,34 +1495,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563872</v>
+        <v>563804</v>
       </c>
       <c r="R9" t="n">
-        <v>7034672</v>
+        <v>7034635</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1569,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,7 +1601,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123331425</v>
+        <v>123332733</v>
       </c>
       <c r="B10" t="n">
         <v>57491</v>
@@ -1627,19 +1637,19 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563804</v>
+        <v>563800</v>
       </c>
       <c r="R10" t="n">
-        <v>7034635</v>
+        <v>7034674</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,12 +1691,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123332733</v>
+        <v>123333247</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,39 +1739,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563800</v>
+        <v>563872</v>
       </c>
       <c r="R11" t="n">
-        <v>7034674</v>
+        <v>7034672</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,12 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2867,10 +2867,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123331329</v>
+        <v>123332362</v>
       </c>
       <c r="B21" t="n">
-        <v>57507</v>
+        <v>92271</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2879,43 +2879,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563811</v>
+        <v>563655</v>
       </c>
       <c r="R21" t="n">
-        <v>7034627</v>
+        <v>7034668</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2947,7 +2942,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2952,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,10 +2979,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123332362</v>
+        <v>123331329</v>
       </c>
       <c r="B22" t="n">
-        <v>92271</v>
+        <v>57507</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2996,38 +2991,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563655</v>
+        <v>563811</v>
       </c>
       <c r="R22" t="n">
-        <v>7034668</v>
+        <v>7034627</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123332312</v>
+        <v>123331364</v>
       </c>
       <c r="B5" t="n">
-        <v>78525</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563656</v>
+        <v>563802</v>
       </c>
       <c r="R5" t="n">
-        <v>7034674</v>
+        <v>7034635</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123331364</v>
+        <v>123332312</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>78525</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1159,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563802</v>
+        <v>563656</v>
       </c>
       <c r="R6" t="n">
-        <v>7034635</v>
+        <v>7034674</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123331425</v>
+        <v>123333247</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,39 +1495,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563804</v>
+        <v>563872</v>
       </c>
       <c r="R9" t="n">
-        <v>7034635</v>
+        <v>7034672</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,12 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,7 +1591,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123332733</v>
+        <v>123331425</v>
       </c>
       <c r="B10" t="n">
         <v>57491</v>
@@ -1637,19 +1627,19 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563800</v>
+        <v>563804</v>
       </c>
       <c r="R10" t="n">
-        <v>7034674</v>
+        <v>7034635</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,12 +1681,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333247</v>
+        <v>123332733</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,34 +1729,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563872</v>
+        <v>563800</v>
       </c>
       <c r="R11" t="n">
-        <v>7034672</v>
+        <v>7034674</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1803,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2419,10 +2419,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333468</v>
+        <v>123331725</v>
       </c>
       <c r="B17" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2435,34 +2435,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563868</v>
+        <v>563771</v>
       </c>
       <c r="R17" t="n">
-        <v>7034642</v>
+        <v>7034644</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2531,7 +2531,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123331725</v>
+        <v>123331912</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2567,14 +2567,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563771</v>
+        <v>563741</v>
       </c>
       <c r="R18" t="n">
-        <v>7034644</v>
+        <v>7034682</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,10 +2643,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123331912</v>
+        <v>123333468</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2659,21 +2659,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563741</v>
+        <v>563868</v>
       </c>
       <c r="R19" t="n">
-        <v>7034682</v>
+        <v>7034642</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2867,10 +2867,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123332362</v>
+        <v>123331329</v>
       </c>
       <c r="B21" t="n">
-        <v>92271</v>
+        <v>57507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2879,38 +2879,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563655</v>
+        <v>563811</v>
       </c>
       <c r="R21" t="n">
-        <v>7034668</v>
+        <v>7034627</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2942,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2952,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123331329</v>
+        <v>123332362</v>
       </c>
       <c r="B22" t="n">
-        <v>57507</v>
+        <v>92271</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,43 +2996,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563811</v>
+        <v>563655</v>
       </c>
       <c r="R22" t="n">
-        <v>7034627</v>
+        <v>7034668</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123331745</v>
+        <v>123333420</v>
       </c>
       <c r="B2" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563774</v>
+        <v>563874</v>
       </c>
       <c r="R2" t="n">
-        <v>7034650</v>
+        <v>7034649</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123331957</v>
+        <v>123331725</v>
       </c>
       <c r="B3" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563744</v>
+        <v>563771</v>
       </c>
       <c r="R3" t="n">
-        <v>7034680</v>
+        <v>7034644</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123331877</v>
+        <v>123332733</v>
       </c>
       <c r="B4" t="n">
-        <v>56692</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,16 +919,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -940,19 +939,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563737</v>
+        <v>563800</v>
       </c>
       <c r="R4" t="n">
-        <v>7034670</v>
+        <v>7034674</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123331364</v>
+        <v>123330924</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>90986</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1041,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563802</v>
+        <v>563880</v>
       </c>
       <c r="R5" t="n">
-        <v>7034635</v>
+        <v>7034641</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123332312</v>
+        <v>123331329</v>
       </c>
       <c r="B6" t="n">
-        <v>78525</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1153,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563656</v>
+        <v>563811</v>
       </c>
       <c r="R6" t="n">
-        <v>7034674</v>
+        <v>7034627</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123331047</v>
+        <v>123331875</v>
       </c>
       <c r="B7" t="n">
-        <v>90986</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,34 +1270,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563862</v>
+        <v>563774</v>
       </c>
       <c r="R7" t="n">
-        <v>7034632</v>
+        <v>7034678</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,22 +1354,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123332192</v>
+        <v>123333247</v>
       </c>
       <c r="B8" t="n">
-        <v>92271</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,38 +1378,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563700</v>
+        <v>563872</v>
       </c>
       <c r="R8" t="n">
-        <v>7034666</v>
+        <v>7034672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333247</v>
+        <v>123333468</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1494,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563872</v>
+        <v>563868</v>
       </c>
       <c r="R9" t="n">
-        <v>7034672</v>
+        <v>7034642</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123331425</v>
+        <v>123331877</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>56692</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,16 +1606,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1627,7 +1626,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1636,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563804</v>
+        <v>563737</v>
       </c>
       <c r="R10" t="n">
-        <v>7034635</v>
+        <v>7034670</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,12 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123332733</v>
+        <v>123331199</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,39 +1723,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563800</v>
+        <v>563848</v>
       </c>
       <c r="R11" t="n">
-        <v>7034674</v>
+        <v>7034634</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,12 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,7 +1819,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123331993</v>
+        <v>123332256</v>
       </c>
       <c r="B12" t="n">
         <v>57491</v>
@@ -1876,14 +1860,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563779</v>
+        <v>563690</v>
       </c>
       <c r="R12" t="n">
-        <v>7034696</v>
+        <v>7034661</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1945,22 +1929,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123331199</v>
+        <v>123332362</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,25 +1953,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1997,10 +1981,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563848</v>
+        <v>563655</v>
       </c>
       <c r="R13" t="n">
-        <v>7034634</v>
+        <v>7034668</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,7 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,10 +2053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333420</v>
+        <v>123331957</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>78524</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,42 +2065,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563874</v>
+        <v>563744</v>
       </c>
       <c r="R14" t="n">
-        <v>7034649</v>
+        <v>7034680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123331795</v>
+        <v>123331047</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2201,34 +2181,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563756</v>
+        <v>563862</v>
       </c>
       <c r="R15" t="n">
-        <v>7034671</v>
+        <v>7034632</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2260,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2250,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,10 +2277,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123332256</v>
+        <v>123331745</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>57644</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,27 +2293,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2342,13 +2322,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563690</v>
+        <v>563774</v>
       </c>
       <c r="R16" t="n">
-        <v>7034661</v>
+        <v>7034650</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2377,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2387,12 +2367,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,22 +2382,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123331725</v>
+        <v>123331364</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2435,34 +2410,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563771</v>
+        <v>563802</v>
       </c>
       <c r="R17" t="n">
-        <v>7034644</v>
+        <v>7034635</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2494,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2504,7 +2484,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2531,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123331912</v>
+        <v>123331425</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2547,34 +2532,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563741</v>
+        <v>563804</v>
       </c>
       <c r="R18" t="n">
-        <v>7034682</v>
+        <v>7034635</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2596,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2606,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,10 +2638,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123333468</v>
+        <v>123331993</v>
       </c>
       <c r="B19" t="n">
-        <v>90990</v>
+        <v>57491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2659,34 +2654,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563868</v>
+        <v>563779</v>
       </c>
       <c r="R19" t="n">
-        <v>7034642</v>
+        <v>7034696</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2728,7 +2728,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,22 +2748,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123331875</v>
+        <v>123332192</v>
       </c>
       <c r="B20" t="n">
-        <v>91008</v>
+        <v>92271</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2767,38 +2772,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563774</v>
+        <v>563700</v>
       </c>
       <c r="R20" t="n">
-        <v>7034678</v>
+        <v>7034666</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2830,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2840,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2855,22 +2860,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123331329</v>
+        <v>123331795</v>
       </c>
       <c r="B21" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2883,39 +2888,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563811</v>
+        <v>563756</v>
       </c>
       <c r="R21" t="n">
-        <v>7034627</v>
+        <v>7034671</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123332362</v>
+        <v>123332312</v>
       </c>
       <c r="B22" t="n">
-        <v>92271</v>
+        <v>78525</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2996,25 +2996,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563655</v>
+        <v>563656</v>
       </c>
       <c r="R22" t="n">
-        <v>7034668</v>
+        <v>7034674</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,10 +3096,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123330924</v>
+        <v>123331912</v>
       </c>
       <c r="B23" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3112,21 +3112,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563880</v>
+        <v>563741</v>
       </c>
       <c r="R23" t="n">
-        <v>7034641</v>
+        <v>7034682</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -1478,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333468</v>
+        <v>123331877</v>
       </c>
       <c r="B9" t="n">
-        <v>90990</v>
+        <v>56692</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,34 +1494,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563868</v>
+        <v>563737</v>
       </c>
       <c r="R9" t="n">
-        <v>7034642</v>
+        <v>7034670</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123331877</v>
+        <v>123333468</v>
       </c>
       <c r="B10" t="n">
-        <v>56692</v>
+        <v>90990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,39 +1611,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563737</v>
+        <v>563868</v>
       </c>
       <c r="R10" t="n">
-        <v>7034670</v>
+        <v>7034642</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123331425</v>
+        <v>123332192</v>
       </c>
       <c r="B18" t="n">
-        <v>57491</v>
+        <v>92271</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,43 +2528,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563804</v>
+        <v>563700</v>
       </c>
       <c r="R18" t="n">
-        <v>7034635</v>
+        <v>7034666</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2596,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,12 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2760,10 +2750,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123332192</v>
+        <v>123331425</v>
       </c>
       <c r="B20" t="n">
-        <v>92271</v>
+        <v>57491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2772,38 +2762,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563700</v>
+        <v>563804</v>
       </c>
       <c r="R20" t="n">
-        <v>7034666</v>
+        <v>7034635</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2835,7 +2830,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2840,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333420</v>
+        <v>123332192</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563874</v>
+        <v>563700</v>
       </c>
       <c r="R2" t="n">
-        <v>7034649</v>
+        <v>7034666</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123331725</v>
+        <v>123331329</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563771</v>
+        <v>563811</v>
       </c>
       <c r="R3" t="n">
-        <v>7034644</v>
+        <v>7034627</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123332733</v>
+        <v>123331875</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563800</v>
+        <v>563774</v>
       </c>
       <c r="R4" t="n">
-        <v>7034674</v>
+        <v>7034678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,12 +1004,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1137,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123331329</v>
+        <v>123333468</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,39 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563811</v>
+        <v>563868</v>
       </c>
       <c r="R6" t="n">
-        <v>7034627</v>
+        <v>7034642</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123331875</v>
+        <v>123331364</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,34 +1256,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563774</v>
+        <v>563802</v>
       </c>
       <c r="R7" t="n">
-        <v>7034678</v>
+        <v>7034635</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1330,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,22 +1350,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333247</v>
+        <v>123331993</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,34 +1378,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563872</v>
+        <v>563779</v>
       </c>
       <c r="R8" t="n">
-        <v>7034672</v>
+        <v>7034696</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1452,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,22 +1472,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123331877</v>
+        <v>123332362</v>
       </c>
       <c r="B9" t="n">
-        <v>56692</v>
+        <v>92271</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,43 +1496,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563737</v>
+        <v>563655</v>
       </c>
       <c r="R9" t="n">
-        <v>7034670</v>
+        <v>7034668</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333468</v>
+        <v>123331047</v>
       </c>
       <c r="B10" t="n">
-        <v>90990</v>
+        <v>90986</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,34 +1612,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563868</v>
+        <v>563862</v>
       </c>
       <c r="R10" t="n">
-        <v>7034642</v>
+        <v>7034632</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,7 +1708,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123331199</v>
+        <v>123331795</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1743,14 +1744,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563848</v>
+        <v>563756</v>
       </c>
       <c r="R11" t="n">
-        <v>7034634</v>
+        <v>7034671</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123332256</v>
+        <v>123331199</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,39 +1836,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563690</v>
+        <v>563848</v>
       </c>
       <c r="R12" t="n">
-        <v>7034661</v>
+        <v>7034634</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,12 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123332362</v>
+        <v>123331425</v>
       </c>
       <c r="B13" t="n">
-        <v>92271</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,38 +1944,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563655</v>
+        <v>563804</v>
       </c>
       <c r="R13" t="n">
-        <v>7034668</v>
+        <v>7034635</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,7 +2022,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123331957</v>
+        <v>123331912</v>
       </c>
       <c r="B14" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,21 +2070,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2093,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563744</v>
+        <v>563741</v>
       </c>
       <c r="R14" t="n">
-        <v>7034680</v>
+        <v>7034682</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123331047</v>
+        <v>123333420</v>
       </c>
       <c r="B15" t="n">
-        <v>90986</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,38 +2178,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563862</v>
+        <v>563874</v>
       </c>
       <c r="R15" t="n">
-        <v>7034632</v>
+        <v>7034649</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2240,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,10 +2282,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123331745</v>
+        <v>123332312</v>
       </c>
       <c r="B16" t="n">
-        <v>57644</v>
+        <v>78525</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,42 +2298,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563774</v>
+        <v>563656</v>
       </c>
       <c r="R16" t="n">
-        <v>7034650</v>
+        <v>7034674</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,19 +2382,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123331364</v>
+        <v>123332256</v>
       </c>
       <c r="B17" t="n">
         <v>57491</v>
@@ -2430,7 +2430,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563802</v>
+        <v>563690</v>
       </c>
       <c r="R17" t="n">
-        <v>7034635</v>
+        <v>7034661</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123332192</v>
+        <v>123331745</v>
       </c>
       <c r="B18" t="n">
-        <v>92271</v>
+        <v>57644</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,41 +2528,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563700</v>
+        <v>563774</v>
       </c>
       <c r="R18" t="n">
-        <v>7034666</v>
+        <v>7034650</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,7 +2596,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,7 +2606,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,22 +2621,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123331993</v>
+        <v>123331877</v>
       </c>
       <c r="B19" t="n">
-        <v>57491</v>
+        <v>56692</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,16 +2649,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2664,19 +2669,19 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563779</v>
+        <v>563737</v>
       </c>
       <c r="R19" t="n">
-        <v>7034696</v>
+        <v>7034670</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2708,7 +2713,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,12 +2723,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,22 +2738,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123331425</v>
+        <v>123331725</v>
       </c>
       <c r="B20" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,39 +2766,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563804</v>
+        <v>563771</v>
       </c>
       <c r="R20" t="n">
-        <v>7034635</v>
+        <v>7034644</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2830,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2840,12 +2835,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,10 +2862,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123331795</v>
+        <v>123332733</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2888,34 +2878,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563756</v>
+        <v>563800</v>
       </c>
       <c r="R21" t="n">
-        <v>7034671</v>
+        <v>7034674</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2947,7 +2942,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2952,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123332312</v>
+        <v>123331957</v>
       </c>
       <c r="B22" t="n">
-        <v>78525</v>
+        <v>78524</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3000,34 +3000,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563656</v>
+        <v>563744</v>
       </c>
       <c r="R22" t="n">
-        <v>7034674</v>
+        <v>7034680</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,7 +3096,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123331912</v>
+        <v>123333247</v>
       </c>
       <c r="B23" t="n">
         <v>78788</v>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563741</v>
+        <v>563872</v>
       </c>
       <c r="R23" t="n">
-        <v>7034682</v>
+        <v>7034672</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123332192</v>
+        <v>123331993</v>
       </c>
       <c r="B2" t="n">
-        <v>92271</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563700</v>
+        <v>563779</v>
       </c>
       <c r="R2" t="n">
-        <v>7034666</v>
+        <v>7034696</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123331329</v>
+        <v>123331745</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,27 +813,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563811</v>
+        <v>563774</v>
       </c>
       <c r="R3" t="n">
-        <v>7034627</v>
+        <v>7034650</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123331875</v>
+        <v>123331877</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>56692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +930,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563774</v>
+        <v>563737</v>
       </c>
       <c r="R4" t="n">
-        <v>7034678</v>
+        <v>7034670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123330924</v>
+        <v>123331875</v>
       </c>
       <c r="B5" t="n">
-        <v>90986</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1047,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563880</v>
+        <v>563774</v>
       </c>
       <c r="R5" t="n">
-        <v>7034641</v>
+        <v>7034678</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333468</v>
+        <v>123331199</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1159,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563868</v>
+        <v>563848</v>
       </c>
       <c r="R6" t="n">
-        <v>7034642</v>
+        <v>7034634</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123331364</v>
+        <v>123330924</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>90986</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563802</v>
+        <v>563880</v>
       </c>
       <c r="R7" t="n">
-        <v>7034635</v>
+        <v>7034641</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,12 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123331993</v>
+        <v>123332362</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
+        <v>92271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,43 +1379,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563779</v>
+        <v>563655</v>
       </c>
       <c r="R8" t="n">
-        <v>7034696</v>
+        <v>7034668</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,12 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123332362</v>
+        <v>123331047</v>
       </c>
       <c r="B9" t="n">
-        <v>92271</v>
+        <v>90986</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,25 +1491,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1524,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563655</v>
+        <v>563862</v>
       </c>
       <c r="R9" t="n">
-        <v>7034668</v>
+        <v>7034632</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123331047</v>
+        <v>123331795</v>
       </c>
       <c r="B10" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,34 +1607,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563862</v>
+        <v>563756</v>
       </c>
       <c r="R10" t="n">
-        <v>7034632</v>
+        <v>7034671</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,7 +1703,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123331795</v>
+        <v>123331912</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1748,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563756</v>
+        <v>563741</v>
       </c>
       <c r="R11" t="n">
-        <v>7034671</v>
+        <v>7034682</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,7 +1815,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123331199</v>
+        <v>123331725</v>
       </c>
       <c r="B12" t="n">
         <v>78788</v>
@@ -1860,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563848</v>
+        <v>563771</v>
       </c>
       <c r="R12" t="n">
-        <v>7034634</v>
+        <v>7034644</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123331425</v>
+        <v>123331329</v>
       </c>
       <c r="B13" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,16 +1943,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1968,7 +1963,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1977,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563804</v>
+        <v>563811</v>
       </c>
       <c r="R13" t="n">
-        <v>7034635</v>
+        <v>7034627</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,12 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123331912</v>
+        <v>123332192</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,38 +2056,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563741</v>
+        <v>563700</v>
       </c>
       <c r="R14" t="n">
-        <v>7034682</v>
+        <v>7034666</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333420</v>
+        <v>123331364</v>
       </c>
       <c r="B15" t="n">
-        <v>98079</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,42 +2168,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563874</v>
+        <v>563802</v>
       </c>
       <c r="R15" t="n">
-        <v>7034649</v>
+        <v>7034635</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2246,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123332312</v>
+        <v>123332256</v>
       </c>
       <c r="B16" t="n">
-        <v>78525</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2298,34 +2294,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563656</v>
+        <v>563690</v>
       </c>
       <c r="R16" t="n">
-        <v>7034674</v>
+        <v>7034661</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,7 +2358,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2368,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123332256</v>
+        <v>123331957</v>
       </c>
       <c r="B17" t="n">
-        <v>57491</v>
+        <v>78524</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2410,39 +2416,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563690</v>
+        <v>563744</v>
       </c>
       <c r="R17" t="n">
-        <v>7034661</v>
+        <v>7034680</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2474,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,12 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123331745</v>
+        <v>123332312</v>
       </c>
       <c r="B18" t="n">
-        <v>57644</v>
+        <v>78525</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,42 +2528,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563774</v>
+        <v>563656</v>
       </c>
       <c r="R18" t="n">
-        <v>7034650</v>
+        <v>7034674</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2596,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,7 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,22 +2612,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123331877</v>
+        <v>123333420</v>
       </c>
       <c r="B19" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2645,43 +2636,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563737</v>
+        <v>563874</v>
       </c>
       <c r="R19" t="n">
-        <v>7034670</v>
+        <v>7034649</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2713,7 +2703,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2723,7 +2713,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2750,10 +2740,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123331725</v>
+        <v>123331425</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,34 +2756,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563771</v>
+        <v>563804</v>
       </c>
       <c r="R20" t="n">
-        <v>7034644</v>
+        <v>7034635</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2825,7 +2820,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,7 +2830,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,10 +2862,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123332733</v>
+        <v>123333247</v>
       </c>
       <c r="B21" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,39 +2878,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563800</v>
+        <v>563872</v>
       </c>
       <c r="R21" t="n">
-        <v>7034674</v>
+        <v>7034672</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2942,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2952,12 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,10 +2974,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123331957</v>
+        <v>123333468</v>
       </c>
       <c r="B22" t="n">
-        <v>78524</v>
+        <v>90990</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3000,21 +2990,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3024,10 +3014,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563744</v>
+        <v>563868</v>
       </c>
       <c r="R22" t="n">
-        <v>7034680</v>
+        <v>7034642</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3059,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,10 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123333247</v>
+        <v>123332733</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3112,34 +3102,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563872</v>
+        <v>563800</v>
       </c>
       <c r="R23" t="n">
-        <v>7034672</v>
+        <v>7034674</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3171,7 +3166,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3176,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123331993</v>
+        <v>123331725</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563779</v>
+        <v>563771</v>
       </c>
       <c r="R2" t="n">
-        <v>7034696</v>
+        <v>7034644</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123331745</v>
+        <v>123331957</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>78524</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,42 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563774</v>
+        <v>563744</v>
       </c>
       <c r="R3" t="n">
-        <v>7034650</v>
+        <v>7034680</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123331877</v>
+        <v>123331425</v>
       </c>
       <c r="B4" t="n">
-        <v>56692</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,16 +915,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563737</v>
+        <v>563804</v>
       </c>
       <c r="R4" t="n">
-        <v>7034670</v>
+        <v>7034635</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123331875</v>
+        <v>123331047</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>90986</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,34 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563774</v>
+        <v>563862</v>
       </c>
       <c r="R5" t="n">
-        <v>7034678</v>
+        <v>7034632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123331199</v>
+        <v>123333468</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563848</v>
+        <v>563868</v>
       </c>
       <c r="R6" t="n">
-        <v>7034634</v>
+        <v>7034642</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123330924</v>
+        <v>123331795</v>
       </c>
       <c r="B7" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563880</v>
+        <v>563756</v>
       </c>
       <c r="R7" t="n">
-        <v>7034641</v>
+        <v>7034671</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123332362</v>
+        <v>123332312</v>
       </c>
       <c r="B8" t="n">
-        <v>92271</v>
+        <v>78525</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563655</v>
+        <v>563656</v>
       </c>
       <c r="R8" t="n">
-        <v>7034668</v>
+        <v>7034674</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123331047</v>
+        <v>123331364</v>
       </c>
       <c r="B9" t="n">
-        <v>90986</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,34 +1485,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563862</v>
+        <v>563802</v>
       </c>
       <c r="R9" t="n">
-        <v>7034632</v>
+        <v>7034635</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1559,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123331795</v>
+        <v>123330924</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563756</v>
+        <v>563880</v>
       </c>
       <c r="R10" t="n">
-        <v>7034671</v>
+        <v>7034641</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123331912</v>
+        <v>123333420</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,38 +1715,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563741</v>
+        <v>563874</v>
       </c>
       <c r="R11" t="n">
-        <v>7034682</v>
+        <v>7034649</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123331725</v>
+        <v>123332192</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,25 +1831,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1859,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563771</v>
+        <v>563700</v>
       </c>
       <c r="R12" t="n">
-        <v>7034644</v>
+        <v>7034666</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1904,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123331329</v>
+        <v>123331993</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,16 +1947,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1963,19 +1967,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563811</v>
+        <v>563779</v>
       </c>
       <c r="R13" t="n">
-        <v>7034627</v>
+        <v>7034696</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2021,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,19 +2041,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123332192</v>
+        <v>123332362</v>
       </c>
       <c r="B14" t="n">
         <v>92271</v>
@@ -2084,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563700</v>
+        <v>563655</v>
       </c>
       <c r="R14" t="n">
-        <v>7034666</v>
+        <v>7034668</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,7 +2165,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123331364</v>
+        <v>123332256</v>
       </c>
       <c r="B15" t="n">
         <v>57491</v>
@@ -2192,7 +2201,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2201,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563802</v>
+        <v>563690</v>
       </c>
       <c r="R15" t="n">
-        <v>7034635</v>
+        <v>7034661</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,12 +2255,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123332256</v>
+        <v>123331745</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>57644</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,27 +2303,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2323,13 +2332,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563690</v>
+        <v>563774</v>
       </c>
       <c r="R16" t="n">
-        <v>7034661</v>
+        <v>7034650</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2358,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2368,12 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,22 +2392,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123331957</v>
+        <v>123331199</v>
       </c>
       <c r="B17" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,34 +2420,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563744</v>
+        <v>563848</v>
       </c>
       <c r="R17" t="n">
-        <v>7034680</v>
+        <v>7034634</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123332312</v>
+        <v>123331912</v>
       </c>
       <c r="B18" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,34 +2532,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563656</v>
+        <v>563741</v>
       </c>
       <c r="R18" t="n">
-        <v>7034674</v>
+        <v>7034682</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,7 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123333420</v>
+        <v>123331875</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>91008</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,42 +2640,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563874</v>
+        <v>563774</v>
       </c>
       <c r="R19" t="n">
-        <v>7034649</v>
+        <v>7034678</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,22 +2728,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123331425</v>
+        <v>123331329</v>
       </c>
       <c r="B20" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2756,16 +2756,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563804</v>
+        <v>563811</v>
       </c>
       <c r="R20" t="n">
-        <v>7034635</v>
+        <v>7034627</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2830,12 +2830,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,10 +2857,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123333247</v>
+        <v>123332733</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,34 +2873,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563872</v>
+        <v>563800</v>
       </c>
       <c r="R21" t="n">
-        <v>7034672</v>
+        <v>7034674</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2947,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,10 +2979,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123333468</v>
+        <v>123333247</v>
       </c>
       <c r="B22" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,21 +2995,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3014,10 +3019,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563868</v>
+        <v>563872</v>
       </c>
       <c r="R22" t="n">
-        <v>7034642</v>
+        <v>7034672</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3049,7 +3054,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3064,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3086,10 +3091,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123332733</v>
+        <v>123331877</v>
       </c>
       <c r="B23" t="n">
-        <v>57491</v>
+        <v>56692</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,16 +3107,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3122,19 +3127,19 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563800</v>
+        <v>563737</v>
       </c>
       <c r="R23" t="n">
-        <v>7034674</v>
+        <v>7034670</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3166,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3176,12 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123331745</v>
+        <v>123330924</v>
       </c>
       <c r="B2" t="n">
-        <v>57644</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563774</v>
+        <v>563880</v>
       </c>
       <c r="R2" t="n">
-        <v>7034650</v>
+        <v>7034641</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123331364</v>
+        <v>123331047</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563802</v>
+        <v>563862</v>
       </c>
       <c r="R3" t="n">
-        <v>7034635</v>
+        <v>7034632</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123332362</v>
+        <v>123333468</v>
       </c>
       <c r="B4" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563655</v>
+        <v>563868</v>
       </c>
       <c r="R4" t="n">
-        <v>7034668</v>
+        <v>7034642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333468</v>
+        <v>123332192</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563868</v>
+        <v>563700</v>
       </c>
       <c r="R5" t="n">
-        <v>7034642</v>
+        <v>7034666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123331957</v>
+        <v>123332362</v>
       </c>
       <c r="B6" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,34 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563744</v>
+        <v>563655</v>
       </c>
       <c r="R6" t="n">
-        <v>7034680</v>
+        <v>7034668</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,55 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123331877</v>
+        <v>123331199</v>
       </c>
       <c r="B7" t="n">
-        <v>56692</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563737</v>
+        <v>563848</v>
       </c>
       <c r="R7" t="n">
-        <v>7034670</v>
+        <v>7034634</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,55 +1317,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123331329</v>
+        <v>123331725</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563811</v>
+        <v>563771</v>
       </c>
       <c r="R8" t="n">
-        <v>7034627</v>
+        <v>7034644</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,50 +1424,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123331047</v>
+        <v>123331795</v>
       </c>
       <c r="B9" t="n">
-        <v>90986</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563862</v>
+        <v>563756</v>
       </c>
       <c r="R9" t="n">
-        <v>7034632</v>
+        <v>7034671</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,37 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123330924</v>
+        <v>123331912</v>
       </c>
       <c r="B10" t="n">
-        <v>90986</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563880</v>
+        <v>563741</v>
       </c>
       <c r="R10" t="n">
-        <v>7034641</v>
+        <v>7034682</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,19 +1638,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123331795</v>
+        <v>123333247</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1748,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563756</v>
+        <v>563872</v>
       </c>
       <c r="R11" t="n">
-        <v>7034671</v>
+        <v>7034672</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,15 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123332256</v>
+        <v>123331957</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,39 +1756,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563690</v>
+        <v>563744</v>
       </c>
       <c r="R12" t="n">
-        <v>7034661</v>
+        <v>7034680</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,12 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,50 +1852,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123331199</v>
+        <v>123331329</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563848</v>
+        <v>563811</v>
       </c>
       <c r="R13" t="n">
-        <v>7034634</v>
+        <v>7034627</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,15 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123331993</v>
+        <v>123331364</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2090,19 +1995,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563779</v>
+        <v>563802</v>
       </c>
       <c r="R14" t="n">
-        <v>7034696</v>
+        <v>7034635</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,12 +2049,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,66 +2069,62 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333420</v>
+        <v>123331425</v>
       </c>
       <c r="B15" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563874</v>
+        <v>563804</v>
       </c>
       <c r="R15" t="n">
-        <v>7034649</v>
+        <v>7034635</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2265,7 +2166,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,15 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123332733</v>
+        <v>123331993</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2229,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2337,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563800</v>
+        <v>563779</v>
       </c>
       <c r="R16" t="n">
-        <v>7034674</v>
+        <v>7034696</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2372,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2402,27 +2303,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123331912</v>
+        <v>123332256</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,34 +2326,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
+          <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563741</v>
+        <v>563690</v>
       </c>
       <c r="R17" t="n">
-        <v>7034682</v>
+        <v>7034661</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2489,7 +2390,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2400,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,15 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123332312</v>
+        <v>123332733</v>
       </c>
       <c r="B18" t="n">
-        <v>78525</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,31 +2443,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vikebodarna, Vikebodarna, Ång</t>
+          <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563656</v>
+        <v>563800</v>
       </c>
       <c r="R18" t="n">
         <v>7034674</v>
@@ -2601,7 +2507,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2611,7 +2517,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2638,50 +2549,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123331725</v>
+        <v>123331877</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563771</v>
+        <v>563737</v>
       </c>
       <c r="R19" t="n">
-        <v>7034644</v>
+        <v>7034670</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2713,7 +2624,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2723,7 +2634,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2750,53 +2661,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123332192</v>
+        <v>123331745</v>
       </c>
       <c r="B20" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563700</v>
+        <v>563774</v>
       </c>
       <c r="R20" t="n">
-        <v>7034666</v>
+        <v>7034650</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2825,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2850,62 +2761,61 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123331875</v>
+        <v>123333420</v>
       </c>
       <c r="B21" t="n">
-        <v>91008</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Middagskullen, Middagskullen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563774</v>
+        <v>563874</v>
       </c>
       <c r="R21" t="n">
-        <v>7034678</v>
+        <v>7034649</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2847,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2857,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2962,27 +2872,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123331425</v>
+        <v>123332312</v>
       </c>
       <c r="B22" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,39 +2895,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vikebodarna, Vikebodarna, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563804</v>
+        <v>563656</v>
       </c>
       <c r="R22" t="n">
-        <v>7034635</v>
+        <v>7034674</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,7 +2954,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3064,12 +2964,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3093,118 +2988,6 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>123333247</v>
-      </c>
-      <c r="B23" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Middagskullen, Middagskullen, Ång</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>563872</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7034672</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Ramsele</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4839-2025 artfynd.xlsx
+++ b/artfynd/A 4839-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330924</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123331047</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333468</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123332192</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123332362</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123331199</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123331725</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123331795</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123331912</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333247</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123331957</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123331329</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2078,6 +2143,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123331364</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2195,6 +2265,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123331425</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2312,6 +2387,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123331993</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2429,6 +2509,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123332256</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2546,6 +2631,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123332733</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2658,6 +2748,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123331877</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2770,6 +2865,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123331745</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2881,6 +2981,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333420</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2988,8 +3093,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123332312</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>